--- a/public/plantilla-capacitacion-ambiental.xlsx
+++ b/public/plantilla-capacitacion-ambiental.xlsx
@@ -15,6 +15,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="1">
+    <numFmt numFmtId="166" formatCode="hh:mm"/>
+  </numFmts>
   <fonts count="20">
     <font>
       <name val="Calibri"/>
@@ -554,19 +557,19 @@
     <xf numFmtId="4" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="167" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="4" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="168" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -615,7 +618,7 @@
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="4" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -668,7 +671,7 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="6" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="167" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">

--- a/public/plantilla-capacitacion-ambiental.xlsx
+++ b/public/plantilla-capacitacion-ambiental.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="9" autoFilterDateGrouping="1"/>
+    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitación Ambiental" sheetId="1" state="visible" r:id="rId1"/>

--- a/public/plantilla-capacitacion-ambiental.xlsx
+++ b/public/plantilla-capacitacion-ambiental.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
-    <workbookView activeTab="0" visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Capacitación Ambiental" sheetId="1" state="visible" r:id="rId1"/>
@@ -16,9 +16,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="1">
-    <numFmt numFmtId="166" formatCode="hh:mm"/>
+    <numFmt numFmtId="164" formatCode="hh:mm"/>
   </numFmts>
-  <fonts count="20">
+  <fonts count="21">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -163,6 +163,10 @@
       <b val="1"/>
       <sz val="9"/>
     </font>
+    <font>
+      <name val="Calibri"/>
+      <sz val="10"/>
+    </font>
   </fonts>
   <fills count="17">
     <fill>
@@ -529,7 +533,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="97">
+  <cellXfs count="110">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="3"/>
     <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -560,7 +564,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="166" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -636,7 +640,7 @@
     <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="left" vertical="center" shrinkToFit="1" indent="1"/>
     </xf>
-    <xf numFmtId="166" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
@@ -757,6 +761,51 @@
     </xf>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="9" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="17" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="9" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="14" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="164" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="5" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <protection locked="0" hidden="0"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="7" applyAlignment="1" applyProtection="1" pivotButton="0" quotePrefix="0" xfId="3">
+      <alignment horizontal="center" vertical="center"/>
+      <protection locked="0" hidden="0"/>
+    </xf>
   </cellXfs>
   <cellStyles count="6">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1219,6 +1268,7 @@
   <cols>
     <col width="12.77734375" customWidth="1" style="27" min="1" max="1"/>
     <col width="13" customWidth="1" style="27" min="2" max="3"/>
+    <col width="13" customWidth="1" style="27" min="3" max="3"/>
     <col width="15.77734375" customWidth="1" style="27" min="4" max="4"/>
     <col width="10" customWidth="1" style="27" min="5" max="5"/>
     <col width="15.77734375" customWidth="1" style="27" min="6" max="6"/>
@@ -1386,16 +1436,16 @@
         </is>
       </c>
       <c r="B11" s="22" t="n"/>
-      <c r="C11" s="24" t="n"/>
-      <c r="D11" s="25" t="n"/>
-      <c r="E11" s="25" t="n"/>
-      <c r="F11" s="25" t="n"/>
-      <c r="G11" s="25" t="n"/>
-      <c r="H11" s="25" t="n"/>
-      <c r="I11" s="25" t="n"/>
-      <c r="J11" s="25" t="n"/>
-      <c r="K11" s="25" t="n"/>
-      <c r="L11" s="22" t="n"/>
+      <c r="C11" s="97" t="n"/>
+      <c r="D11" s="98" t="n"/>
+      <c r="E11" s="98" t="n"/>
+      <c r="F11" s="98" t="n"/>
+      <c r="G11" s="98" t="n"/>
+      <c r="H11" s="98" t="n"/>
+      <c r="I11" s="98" t="n"/>
+      <c r="J11" s="98" t="n"/>
+      <c r="K11" s="98" t="n"/>
+      <c r="L11" s="99" t="n"/>
     </row>
     <row r="12" ht="21" customHeight="1" s="27">
       <c r="A12" s="88" t="inlineStr">
@@ -1404,20 +1454,20 @@
         </is>
       </c>
       <c r="B12" s="22" t="n"/>
-      <c r="C12" s="24" t="n"/>
-      <c r="D12" s="25" t="n"/>
-      <c r="E12" s="25" t="n"/>
-      <c r="F12" s="25" t="n"/>
-      <c r="G12" s="22" t="n"/>
+      <c r="C12" s="97" t="n"/>
+      <c r="D12" s="98" t="n"/>
+      <c r="E12" s="98" t="n"/>
+      <c r="F12" s="98" t="n"/>
+      <c r="G12" s="99" t="n"/>
       <c r="H12" s="88" t="inlineStr">
         <is>
           <t>Ubicación</t>
         </is>
       </c>
       <c r="I12" s="22" t="n"/>
-      <c r="J12" s="24" t="n"/>
-      <c r="K12" s="25" t="n"/>
-      <c r="L12" s="22" t="n"/>
+      <c r="J12" s="97" t="n"/>
+      <c r="K12" s="98" t="n"/>
+      <c r="L12" s="99" t="n"/>
     </row>
     <row r="13" ht="21" customHeight="1" s="27">
       <c r="A13" s="88" t="inlineStr">
@@ -1426,24 +1476,24 @@
         </is>
       </c>
       <c r="B13" s="22" t="n"/>
-      <c r="C13" s="23" t="n"/>
-      <c r="D13" s="22" t="n"/>
+      <c r="C13" s="100" t="n"/>
+      <c r="D13" s="99" t="n"/>
       <c r="E13" s="88" t="inlineStr">
         <is>
           <t>Hora de inicio</t>
         </is>
       </c>
       <c r="F13" s="22" t="n"/>
-      <c r="G13" s="44" t="n"/>
-      <c r="H13" s="22" t="n"/>
+      <c r="G13" s="101" t="n"/>
+      <c r="H13" s="99" t="n"/>
       <c r="I13" s="88" t="inlineStr">
         <is>
           <t>Hora de fin</t>
         </is>
       </c>
       <c r="J13" s="22" t="n"/>
-      <c r="K13" s="44" t="n"/>
-      <c r="L13" s="22" t="n"/>
+      <c r="K13" s="101" t="n"/>
+      <c r="L13" s="99" t="n"/>
     </row>
     <row r="14" ht="21" customHeight="1" s="27">
       <c r="A14" s="88" t="inlineStr">
@@ -1452,18 +1502,18 @@
         </is>
       </c>
       <c r="B14" s="22" t="n"/>
-      <c r="C14" s="24" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
-      <c r="G14" s="22" t="n"/>
+      <c r="C14" s="97" t="n"/>
+      <c r="D14" s="98" t="n"/>
+      <c r="E14" s="98" t="n"/>
+      <c r="F14" s="98" t="n"/>
+      <c r="G14" s="99" t="n"/>
       <c r="H14" s="88" t="inlineStr">
         <is>
           <t>Duración</t>
         </is>
       </c>
       <c r="I14" s="22" t="n"/>
-      <c r="J14" s="32">
+      <c r="J14" s="102">
         <f>IF(OR(G13="",K13=""),"",TEXT(K13-G13,"h:mm")&amp;" h")</f>
         <v/>
       </c>
@@ -1489,28 +1539,28 @@
       <c r="L15" s="18" t="n"/>
     </row>
     <row r="16" ht="18" customHeight="1" s="27">
-      <c r="A16" s="16" t="inlineStr">
+      <c r="A16" s="103" t="inlineStr">
         <is>
           <t>☐ Inducción ambiental (personal nuevo)</t>
         </is>
       </c>
       <c r="B16" s="17" t="n"/>
       <c r="C16" s="18" t="n"/>
-      <c r="D16" s="16" t="inlineStr">
+      <c r="D16" s="103" t="inlineStr">
         <is>
           <t>☐ Capacitación ambiental</t>
         </is>
       </c>
       <c r="E16" s="17" t="n"/>
       <c r="F16" s="18" t="n"/>
-      <c r="G16" s="16" t="inlineStr">
+      <c r="G16" s="103" t="inlineStr">
         <is>
           <t>☐ Charla ambiental (5 minutos)</t>
         </is>
       </c>
       <c r="H16" s="17" t="n"/>
       <c r="I16" s="18" t="n"/>
-      <c r="J16" s="16" t="inlineStr">
+      <c r="J16" s="103" t="inlineStr">
         <is>
           <t>☐ Sensibilización a la comunidad</t>
         </is>
@@ -1537,7 +1587,7 @@
       <c r="L17" s="85" t="n"/>
     </row>
     <row r="18" ht="18" customHeight="1" s="27">
-      <c r="A18" s="16" t="inlineStr">
+      <c r="A18" s="103" t="inlineStr">
         <is>
           <t>☐ Manejo y separación de residuos</t>
         </is>
@@ -1545,7 +1595,7 @@
       <c r="B18" s="17" t="n"/>
       <c r="C18" s="17" t="n"/>
       <c r="D18" s="18" t="n"/>
-      <c r="E18" s="16" t="inlineStr">
+      <c r="E18" s="103" t="inlineStr">
         <is>
           <t>☐ Escombros y RCD</t>
         </is>
@@ -1553,7 +1603,7 @@
       <c r="F18" s="17" t="n"/>
       <c r="G18" s="17" t="n"/>
       <c r="H18" s="18" t="n"/>
-      <c r="I18" s="16" t="inlineStr">
+      <c r="I18" s="103" t="inlineStr">
         <is>
           <t>☐ Uso eficiente del agua</t>
         </is>
@@ -1563,7 +1613,7 @@
       <c r="L18" s="18" t="n"/>
     </row>
     <row r="19" ht="18" customHeight="1" s="27">
-      <c r="A19" s="16" t="inlineStr">
+      <c r="A19" s="103" t="inlineStr">
         <is>
           <t>☐ Uso eficiente de la energía</t>
         </is>
@@ -1571,7 +1621,7 @@
       <c r="B19" s="17" t="n"/>
       <c r="C19" s="17" t="n"/>
       <c r="D19" s="18" t="n"/>
-      <c r="E19" s="16" t="inlineStr">
+      <c r="E19" s="103" t="inlineStr">
         <is>
           <t>☐ Derrames y atención de contingencias</t>
         </is>
@@ -1579,7 +1629,7 @@
       <c r="F19" s="17" t="n"/>
       <c r="G19" s="17" t="n"/>
       <c r="H19" s="18" t="n"/>
-      <c r="I19" s="16" t="inlineStr">
+      <c r="I19" s="103" t="inlineStr">
         <is>
           <t>☐ Manejo de combustibles y químicos</t>
         </is>
@@ -1589,7 +1639,7 @@
       <c r="L19" s="18" t="n"/>
     </row>
     <row r="20" ht="18" customHeight="1" s="27">
-      <c r="A20" s="16" t="inlineStr">
+      <c r="A20" s="103" t="inlineStr">
         <is>
           <t>☐ Control de polvo y ruido</t>
         </is>
@@ -1597,7 +1647,7 @@
       <c r="B20" s="17" t="n"/>
       <c r="C20" s="17" t="n"/>
       <c r="D20" s="18" t="n"/>
-      <c r="E20" s="16" t="inlineStr">
+      <c r="E20" s="103" t="inlineStr">
         <is>
           <t>☐ Protección de fauna y flora</t>
         </is>
@@ -1605,7 +1655,7 @@
       <c r="F20" s="17" t="n"/>
       <c r="G20" s="17" t="n"/>
       <c r="H20" s="18" t="n"/>
-      <c r="I20" s="16" t="inlineStr">
+      <c r="I20" s="103" t="inlineStr">
         <is>
           <t>☐ Normas y permisos ambientales</t>
         </is>
@@ -1615,7 +1665,7 @@
       <c r="L20" s="18" t="n"/>
     </row>
     <row r="21" ht="18" customHeight="1" s="27">
-      <c r="A21" s="16" t="inlineStr">
+      <c r="A21" s="103" t="inlineStr">
         <is>
           <t>☐ Relación con la comunidad</t>
         </is>
@@ -1623,7 +1673,7 @@
       <c r="B21" s="17" t="n"/>
       <c r="C21" s="17" t="n"/>
       <c r="D21" s="18" t="n"/>
-      <c r="E21" s="16" t="inlineStr">
+      <c r="E21" s="103" t="inlineStr">
         <is>
           <t>☐ Plan de manejo ambiental de la obra</t>
         </is>
@@ -1631,7 +1681,7 @@
       <c r="F21" s="17" t="n"/>
       <c r="G21" s="17" t="n"/>
       <c r="H21" s="18" t="n"/>
-      <c r="I21" s="16" t="inlineStr">
+      <c r="I21" s="103" t="inlineStr">
         <is>
           <t>☐ Otro:</t>
         </is>
@@ -1647,20 +1697,20 @@
         </is>
       </c>
       <c r="B22" s="22" t="n"/>
-      <c r="C22" s="24" t="n"/>
-      <c r="D22" s="25" t="n"/>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
-      <c r="G22" s="22" t="n"/>
+      <c r="C22" s="97" t="n"/>
+      <c r="D22" s="98" t="n"/>
+      <c r="E22" s="98" t="n"/>
+      <c r="F22" s="98" t="n"/>
+      <c r="G22" s="99" t="n"/>
       <c r="H22" s="88" t="inlineStr">
         <is>
           <t>Cargo o entidad</t>
         </is>
       </c>
       <c r="I22" s="22" t="n"/>
-      <c r="J22" s="24" t="n"/>
-      <c r="K22" s="25" t="n"/>
-      <c r="L22" s="22" t="n"/>
+      <c r="J22" s="97" t="n"/>
+      <c r="K22" s="98" t="n"/>
+      <c r="L22" s="99" t="n"/>
     </row>
     <row r="23" ht="48" customHeight="1" s="27">
       <c r="A23" s="88" t="inlineStr">
@@ -1669,16 +1719,16 @@
         </is>
       </c>
       <c r="B23" s="22" t="n"/>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-      <c r="G23" s="25" t="n"/>
-      <c r="H23" s="25" t="n"/>
-      <c r="I23" s="25" t="n"/>
-      <c r="J23" s="25" t="n"/>
-      <c r="K23" s="25" t="n"/>
-      <c r="L23" s="22" t="n"/>
+      <c r="C23" s="104" t="n"/>
+      <c r="D23" s="98" t="n"/>
+      <c r="E23" s="98" t="n"/>
+      <c r="F23" s="98" t="n"/>
+      <c r="G23" s="98" t="n"/>
+      <c r="H23" s="98" t="n"/>
+      <c r="I23" s="98" t="n"/>
+      <c r="J23" s="98" t="n"/>
+      <c r="K23" s="98" t="n"/>
+      <c r="L23" s="99" t="n"/>
     </row>
     <row r="24" ht="16.5" customHeight="1" s="27">
       <c r="A24" s="77" t="inlineStr">
@@ -1733,324 +1783,324 @@
       <c r="L25" s="21" t="n"/>
     </row>
     <row r="26" ht="24" customHeight="1" s="27">
-      <c r="A26" s="41" t="n">
+      <c r="A26" s="105" t="n">
         <v>1</v>
       </c>
-      <c r="B26" s="16" t="n"/>
-      <c r="C26" s="17" t="n"/>
-      <c r="D26" s="17" t="n"/>
-      <c r="E26" s="18" t="n"/>
-      <c r="F26" s="41" t="n"/>
-      <c r="G26" s="18" t="n"/>
-      <c r="H26" s="16" t="n"/>
-      <c r="I26" s="18" t="n"/>
-      <c r="J26" s="43" t="n"/>
-      <c r="K26" s="17" t="n"/>
-      <c r="L26" s="18" t="n"/>
+      <c r="B26" s="106" t="n"/>
+      <c r="C26" s="107" t="n"/>
+      <c r="D26" s="107" t="n"/>
+      <c r="E26" s="108" t="n"/>
+      <c r="F26" s="109" t="n"/>
+      <c r="G26" s="108" t="n"/>
+      <c r="H26" s="106" t="n"/>
+      <c r="I26" s="108" t="n"/>
+      <c r="J26" s="106" t="n"/>
+      <c r="K26" s="107" t="n"/>
+      <c r="L26" s="108" t="n"/>
     </row>
     <row r="27" ht="24" customHeight="1" s="27">
-      <c r="A27" s="41" t="n">
+      <c r="A27" s="105" t="n">
         <v>2</v>
       </c>
-      <c r="B27" s="16" t="n"/>
-      <c r="C27" s="17" t="n"/>
-      <c r="D27" s="17" t="n"/>
-      <c r="E27" s="18" t="n"/>
-      <c r="F27" s="41" t="n"/>
-      <c r="G27" s="18" t="n"/>
-      <c r="H27" s="16" t="n"/>
-      <c r="I27" s="18" t="n"/>
-      <c r="J27" s="43" t="n"/>
-      <c r="K27" s="17" t="n"/>
-      <c r="L27" s="18" t="n"/>
+      <c r="B27" s="106" t="n"/>
+      <c r="C27" s="107" t="n"/>
+      <c r="D27" s="107" t="n"/>
+      <c r="E27" s="108" t="n"/>
+      <c r="F27" s="109" t="n"/>
+      <c r="G27" s="108" t="n"/>
+      <c r="H27" s="106" t="n"/>
+      <c r="I27" s="108" t="n"/>
+      <c r="J27" s="106" t="n"/>
+      <c r="K27" s="107" t="n"/>
+      <c r="L27" s="108" t="n"/>
     </row>
     <row r="28" ht="24" customHeight="1" s="27">
-      <c r="A28" s="41" t="n">
+      <c r="A28" s="105" t="n">
         <v>3</v>
       </c>
-      <c r="B28" s="16" t="n"/>
-      <c r="C28" s="17" t="n"/>
-      <c r="D28" s="17" t="n"/>
-      <c r="E28" s="18" t="n"/>
-      <c r="F28" s="41" t="n"/>
-      <c r="G28" s="18" t="n"/>
-      <c r="H28" s="16" t="n"/>
-      <c r="I28" s="18" t="n"/>
-      <c r="J28" s="43" t="n"/>
-      <c r="K28" s="17" t="n"/>
-      <c r="L28" s="18" t="n"/>
+      <c r="B28" s="106" t="n"/>
+      <c r="C28" s="107" t="n"/>
+      <c r="D28" s="107" t="n"/>
+      <c r="E28" s="108" t="n"/>
+      <c r="F28" s="109" t="n"/>
+      <c r="G28" s="108" t="n"/>
+      <c r="H28" s="106" t="n"/>
+      <c r="I28" s="108" t="n"/>
+      <c r="J28" s="106" t="n"/>
+      <c r="K28" s="107" t="n"/>
+      <c r="L28" s="108" t="n"/>
     </row>
     <row r="29" ht="24" customHeight="1" s="27">
-      <c r="A29" s="41" t="n">
+      <c r="A29" s="105" t="n">
         <v>4</v>
       </c>
-      <c r="B29" s="16" t="n"/>
-      <c r="C29" s="17" t="n"/>
-      <c r="D29" s="17" t="n"/>
-      <c r="E29" s="18" t="n"/>
-      <c r="F29" s="41" t="n"/>
-      <c r="G29" s="18" t="n"/>
-      <c r="H29" s="16" t="n"/>
-      <c r="I29" s="18" t="n"/>
-      <c r="J29" s="43" t="n"/>
-      <c r="K29" s="17" t="n"/>
-      <c r="L29" s="18" t="n"/>
+      <c r="B29" s="106" t="n"/>
+      <c r="C29" s="107" t="n"/>
+      <c r="D29" s="107" t="n"/>
+      <c r="E29" s="108" t="n"/>
+      <c r="F29" s="109" t="n"/>
+      <c r="G29" s="108" t="n"/>
+      <c r="H29" s="106" t="n"/>
+      <c r="I29" s="108" t="n"/>
+      <c r="J29" s="106" t="n"/>
+      <c r="K29" s="107" t="n"/>
+      <c r="L29" s="108" t="n"/>
     </row>
     <row r="30" ht="24" customHeight="1" s="27">
-      <c r="A30" s="41" t="n">
+      <c r="A30" s="105" t="n">
         <v>5</v>
       </c>
-      <c r="B30" s="16" t="n"/>
-      <c r="C30" s="17" t="n"/>
-      <c r="D30" s="17" t="n"/>
-      <c r="E30" s="18" t="n"/>
-      <c r="F30" s="41" t="n"/>
-      <c r="G30" s="18" t="n"/>
-      <c r="H30" s="16" t="n"/>
-      <c r="I30" s="18" t="n"/>
-      <c r="J30" s="43" t="n"/>
-      <c r="K30" s="17" t="n"/>
-      <c r="L30" s="18" t="n"/>
+      <c r="B30" s="106" t="n"/>
+      <c r="C30" s="107" t="n"/>
+      <c r="D30" s="107" t="n"/>
+      <c r="E30" s="108" t="n"/>
+      <c r="F30" s="109" t="n"/>
+      <c r="G30" s="108" t="n"/>
+      <c r="H30" s="106" t="n"/>
+      <c r="I30" s="108" t="n"/>
+      <c r="J30" s="106" t="n"/>
+      <c r="K30" s="107" t="n"/>
+      <c r="L30" s="108" t="n"/>
     </row>
     <row r="31" ht="24" customHeight="1" s="27">
-      <c r="A31" s="41" t="n">
+      <c r="A31" s="105" t="n">
         <v>6</v>
       </c>
-      <c r="B31" s="16" t="n"/>
-      <c r="C31" s="17" t="n"/>
-      <c r="D31" s="17" t="n"/>
-      <c r="E31" s="18" t="n"/>
-      <c r="F31" s="41" t="n"/>
-      <c r="G31" s="18" t="n"/>
-      <c r="H31" s="16" t="n"/>
-      <c r="I31" s="18" t="n"/>
-      <c r="J31" s="43" t="n"/>
-      <c r="K31" s="17" t="n"/>
-      <c r="L31" s="18" t="n"/>
+      <c r="B31" s="106" t="n"/>
+      <c r="C31" s="107" t="n"/>
+      <c r="D31" s="107" t="n"/>
+      <c r="E31" s="108" t="n"/>
+      <c r="F31" s="109" t="n"/>
+      <c r="G31" s="108" t="n"/>
+      <c r="H31" s="106" t="n"/>
+      <c r="I31" s="108" t="n"/>
+      <c r="J31" s="106" t="n"/>
+      <c r="K31" s="107" t="n"/>
+      <c r="L31" s="108" t="n"/>
     </row>
     <row r="32" ht="24" customHeight="1" s="27">
-      <c r="A32" s="41" t="n">
+      <c r="A32" s="105" t="n">
         <v>7</v>
       </c>
-      <c r="B32" s="16" t="n"/>
-      <c r="C32" s="17" t="n"/>
-      <c r="D32" s="17" t="n"/>
-      <c r="E32" s="18" t="n"/>
-      <c r="F32" s="41" t="n"/>
-      <c r="G32" s="18" t="n"/>
-      <c r="H32" s="16" t="n"/>
-      <c r="I32" s="18" t="n"/>
-      <c r="J32" s="43" t="n"/>
-      <c r="K32" s="17" t="n"/>
-      <c r="L32" s="18" t="n"/>
+      <c r="B32" s="106" t="n"/>
+      <c r="C32" s="107" t="n"/>
+      <c r="D32" s="107" t="n"/>
+      <c r="E32" s="108" t="n"/>
+      <c r="F32" s="109" t="n"/>
+      <c r="G32" s="108" t="n"/>
+      <c r="H32" s="106" t="n"/>
+      <c r="I32" s="108" t="n"/>
+      <c r="J32" s="106" t="n"/>
+      <c r="K32" s="107" t="n"/>
+      <c r="L32" s="108" t="n"/>
     </row>
     <row r="33" ht="24" customHeight="1" s="27">
-      <c r="A33" s="41" t="n">
+      <c r="A33" s="105" t="n">
         <v>8</v>
       </c>
-      <c r="B33" s="16" t="n"/>
-      <c r="C33" s="17" t="n"/>
-      <c r="D33" s="17" t="n"/>
-      <c r="E33" s="18" t="n"/>
-      <c r="F33" s="41" t="n"/>
-      <c r="G33" s="18" t="n"/>
-      <c r="H33" s="16" t="n"/>
-      <c r="I33" s="18" t="n"/>
-      <c r="J33" s="43" t="n"/>
-      <c r="K33" s="17" t="n"/>
-      <c r="L33" s="18" t="n"/>
+      <c r="B33" s="106" t="n"/>
+      <c r="C33" s="107" t="n"/>
+      <c r="D33" s="107" t="n"/>
+      <c r="E33" s="108" t="n"/>
+      <c r="F33" s="109" t="n"/>
+      <c r="G33" s="108" t="n"/>
+      <c r="H33" s="106" t="n"/>
+      <c r="I33" s="108" t="n"/>
+      <c r="J33" s="106" t="n"/>
+      <c r="K33" s="107" t="n"/>
+      <c r="L33" s="108" t="n"/>
     </row>
     <row r="34" ht="24" customHeight="1" s="27">
-      <c r="A34" s="41" t="n">
+      <c r="A34" s="105" t="n">
         <v>9</v>
       </c>
-      <c r="B34" s="16" t="n"/>
-      <c r="C34" s="17" t="n"/>
-      <c r="D34" s="17" t="n"/>
-      <c r="E34" s="18" t="n"/>
-      <c r="F34" s="41" t="n"/>
-      <c r="G34" s="18" t="n"/>
-      <c r="H34" s="16" t="n"/>
-      <c r="I34" s="18" t="n"/>
-      <c r="J34" s="43" t="n"/>
-      <c r="K34" s="17" t="n"/>
-      <c r="L34" s="18" t="n"/>
+      <c r="B34" s="106" t="n"/>
+      <c r="C34" s="107" t="n"/>
+      <c r="D34" s="107" t="n"/>
+      <c r="E34" s="108" t="n"/>
+      <c r="F34" s="109" t="n"/>
+      <c r="G34" s="108" t="n"/>
+      <c r="H34" s="106" t="n"/>
+      <c r="I34" s="108" t="n"/>
+      <c r="J34" s="106" t="n"/>
+      <c r="K34" s="107" t="n"/>
+      <c r="L34" s="108" t="n"/>
     </row>
     <row r="35" ht="24" customHeight="1" s="27">
-      <c r="A35" s="41" t="n">
+      <c r="A35" s="105" t="n">
         <v>10</v>
       </c>
-      <c r="B35" s="16" t="n"/>
-      <c r="C35" s="17" t="n"/>
-      <c r="D35" s="17" t="n"/>
-      <c r="E35" s="18" t="n"/>
-      <c r="F35" s="41" t="n"/>
-      <c r="G35" s="18" t="n"/>
-      <c r="H35" s="16" t="n"/>
-      <c r="I35" s="18" t="n"/>
-      <c r="J35" s="43" t="n"/>
-      <c r="K35" s="17" t="n"/>
-      <c r="L35" s="18" t="n"/>
+      <c r="B35" s="106" t="n"/>
+      <c r="C35" s="107" t="n"/>
+      <c r="D35" s="107" t="n"/>
+      <c r="E35" s="108" t="n"/>
+      <c r="F35" s="109" t="n"/>
+      <c r="G35" s="108" t="n"/>
+      <c r="H35" s="106" t="n"/>
+      <c r="I35" s="108" t="n"/>
+      <c r="J35" s="106" t="n"/>
+      <c r="K35" s="107" t="n"/>
+      <c r="L35" s="108" t="n"/>
     </row>
     <row r="36" ht="24" customHeight="1" s="27">
-      <c r="A36" s="41" t="n">
+      <c r="A36" s="105" t="n">
         <v>11</v>
       </c>
-      <c r="B36" s="16" t="n"/>
-      <c r="C36" s="17" t="n"/>
-      <c r="D36" s="17" t="n"/>
-      <c r="E36" s="18" t="n"/>
-      <c r="F36" s="41" t="n"/>
-      <c r="G36" s="18" t="n"/>
-      <c r="H36" s="16" t="n"/>
-      <c r="I36" s="18" t="n"/>
-      <c r="J36" s="43" t="n"/>
-      <c r="K36" s="17" t="n"/>
-      <c r="L36" s="18" t="n"/>
+      <c r="B36" s="106" t="n"/>
+      <c r="C36" s="107" t="n"/>
+      <c r="D36" s="107" t="n"/>
+      <c r="E36" s="108" t="n"/>
+      <c r="F36" s="109" t="n"/>
+      <c r="G36" s="108" t="n"/>
+      <c r="H36" s="106" t="n"/>
+      <c r="I36" s="108" t="n"/>
+      <c r="J36" s="106" t="n"/>
+      <c r="K36" s="107" t="n"/>
+      <c r="L36" s="108" t="n"/>
     </row>
     <row r="37" ht="24" customHeight="1" s="27">
-      <c r="A37" s="41" t="n">
+      <c r="A37" s="105" t="n">
         <v>12</v>
       </c>
-      <c r="B37" s="16" t="n"/>
-      <c r="C37" s="17" t="n"/>
-      <c r="D37" s="17" t="n"/>
-      <c r="E37" s="18" t="n"/>
-      <c r="F37" s="41" t="n"/>
-      <c r="G37" s="18" t="n"/>
-      <c r="H37" s="16" t="n"/>
-      <c r="I37" s="18" t="n"/>
-      <c r="J37" s="43" t="n"/>
-      <c r="K37" s="17" t="n"/>
-      <c r="L37" s="18" t="n"/>
+      <c r="B37" s="106" t="n"/>
+      <c r="C37" s="107" t="n"/>
+      <c r="D37" s="107" t="n"/>
+      <c r="E37" s="108" t="n"/>
+      <c r="F37" s="109" t="n"/>
+      <c r="G37" s="108" t="n"/>
+      <c r="H37" s="106" t="n"/>
+      <c r="I37" s="108" t="n"/>
+      <c r="J37" s="106" t="n"/>
+      <c r="K37" s="107" t="n"/>
+      <c r="L37" s="108" t="n"/>
     </row>
     <row r="38" ht="24" customHeight="1" s="27">
-      <c r="A38" s="41" t="n">
+      <c r="A38" s="105" t="n">
         <v>13</v>
       </c>
-      <c r="B38" s="16" t="n"/>
-      <c r="C38" s="17" t="n"/>
-      <c r="D38" s="17" t="n"/>
-      <c r="E38" s="18" t="n"/>
-      <c r="F38" s="41" t="n"/>
-      <c r="G38" s="18" t="n"/>
-      <c r="H38" s="16" t="n"/>
-      <c r="I38" s="18" t="n"/>
-      <c r="J38" s="43" t="n"/>
-      <c r="K38" s="17" t="n"/>
-      <c r="L38" s="18" t="n"/>
+      <c r="B38" s="106" t="n"/>
+      <c r="C38" s="107" t="n"/>
+      <c r="D38" s="107" t="n"/>
+      <c r="E38" s="108" t="n"/>
+      <c r="F38" s="109" t="n"/>
+      <c r="G38" s="108" t="n"/>
+      <c r="H38" s="106" t="n"/>
+      <c r="I38" s="108" t="n"/>
+      <c r="J38" s="106" t="n"/>
+      <c r="K38" s="107" t="n"/>
+      <c r="L38" s="108" t="n"/>
     </row>
     <row r="39" ht="24" customHeight="1" s="27">
-      <c r="A39" s="41" t="n">
+      <c r="A39" s="105" t="n">
         <v>14</v>
       </c>
-      <c r="B39" s="16" t="n"/>
-      <c r="C39" s="17" t="n"/>
-      <c r="D39" s="17" t="n"/>
-      <c r="E39" s="18" t="n"/>
-      <c r="F39" s="41" t="n"/>
-      <c r="G39" s="18" t="n"/>
-      <c r="H39" s="16" t="n"/>
-      <c r="I39" s="18" t="n"/>
-      <c r="J39" s="43" t="n"/>
-      <c r="K39" s="17" t="n"/>
-      <c r="L39" s="18" t="n"/>
+      <c r="B39" s="106" t="n"/>
+      <c r="C39" s="107" t="n"/>
+      <c r="D39" s="107" t="n"/>
+      <c r="E39" s="108" t="n"/>
+      <c r="F39" s="109" t="n"/>
+      <c r="G39" s="108" t="n"/>
+      <c r="H39" s="106" t="n"/>
+      <c r="I39" s="108" t="n"/>
+      <c r="J39" s="106" t="n"/>
+      <c r="K39" s="107" t="n"/>
+      <c r="L39" s="108" t="n"/>
     </row>
     <row r="40" ht="24" customHeight="1" s="27">
-      <c r="A40" s="41" t="n">
+      <c r="A40" s="105" t="n">
         <v>15</v>
       </c>
-      <c r="B40" s="16" t="n"/>
-      <c r="C40" s="17" t="n"/>
-      <c r="D40" s="17" t="n"/>
-      <c r="E40" s="18" t="n"/>
-      <c r="F40" s="41" t="n"/>
-      <c r="G40" s="18" t="n"/>
-      <c r="H40" s="16" t="n"/>
-      <c r="I40" s="18" t="n"/>
-      <c r="J40" s="43" t="n"/>
-      <c r="K40" s="17" t="n"/>
-      <c r="L40" s="18" t="n"/>
+      <c r="B40" s="106" t="n"/>
+      <c r="C40" s="107" t="n"/>
+      <c r="D40" s="107" t="n"/>
+      <c r="E40" s="108" t="n"/>
+      <c r="F40" s="109" t="n"/>
+      <c r="G40" s="108" t="n"/>
+      <c r="H40" s="106" t="n"/>
+      <c r="I40" s="108" t="n"/>
+      <c r="J40" s="106" t="n"/>
+      <c r="K40" s="107" t="n"/>
+      <c r="L40" s="108" t="n"/>
     </row>
     <row r="41" ht="24" customHeight="1" s="27">
-      <c r="A41" s="41" t="n">
+      <c r="A41" s="105" t="n">
         <v>16</v>
       </c>
-      <c r="B41" s="16" t="n"/>
-      <c r="C41" s="17" t="n"/>
-      <c r="D41" s="17" t="n"/>
-      <c r="E41" s="18" t="n"/>
-      <c r="F41" s="41" t="n"/>
-      <c r="G41" s="18" t="n"/>
-      <c r="H41" s="16" t="n"/>
-      <c r="I41" s="18" t="n"/>
-      <c r="J41" s="43" t="n"/>
-      <c r="K41" s="17" t="n"/>
-      <c r="L41" s="18" t="n"/>
+      <c r="B41" s="106" t="n"/>
+      <c r="C41" s="107" t="n"/>
+      <c r="D41" s="107" t="n"/>
+      <c r="E41" s="108" t="n"/>
+      <c r="F41" s="109" t="n"/>
+      <c r="G41" s="108" t="n"/>
+      <c r="H41" s="106" t="n"/>
+      <c r="I41" s="108" t="n"/>
+      <c r="J41" s="106" t="n"/>
+      <c r="K41" s="107" t="n"/>
+      <c r="L41" s="108" t="n"/>
     </row>
     <row r="42" ht="24" customHeight="1" s="27">
-      <c r="A42" s="41" t="n">
+      <c r="A42" s="105" t="n">
         <v>17</v>
       </c>
-      <c r="B42" s="16" t="n"/>
-      <c r="C42" s="17" t="n"/>
-      <c r="D42" s="17" t="n"/>
-      <c r="E42" s="18" t="n"/>
-      <c r="F42" s="41" t="n"/>
-      <c r="G42" s="18" t="n"/>
-      <c r="H42" s="16" t="n"/>
-      <c r="I42" s="18" t="n"/>
-      <c r="J42" s="43" t="n"/>
-      <c r="K42" s="17" t="n"/>
-      <c r="L42" s="18" t="n"/>
+      <c r="B42" s="106" t="n"/>
+      <c r="C42" s="107" t="n"/>
+      <c r="D42" s="107" t="n"/>
+      <c r="E42" s="108" t="n"/>
+      <c r="F42" s="109" t="n"/>
+      <c r="G42" s="108" t="n"/>
+      <c r="H42" s="106" t="n"/>
+      <c r="I42" s="108" t="n"/>
+      <c r="J42" s="106" t="n"/>
+      <c r="K42" s="107" t="n"/>
+      <c r="L42" s="108" t="n"/>
     </row>
     <row r="43" ht="24" customHeight="1" s="27">
-      <c r="A43" s="41" t="n">
+      <c r="A43" s="105" t="n">
         <v>18</v>
       </c>
-      <c r="B43" s="16" t="n"/>
-      <c r="C43" s="17" t="n"/>
-      <c r="D43" s="17" t="n"/>
-      <c r="E43" s="18" t="n"/>
-      <c r="F43" s="41" t="n"/>
-      <c r="G43" s="18" t="n"/>
-      <c r="H43" s="16" t="n"/>
-      <c r="I43" s="18" t="n"/>
-      <c r="J43" s="43" t="n"/>
-      <c r="K43" s="17" t="n"/>
-      <c r="L43" s="18" t="n"/>
+      <c r="B43" s="106" t="n"/>
+      <c r="C43" s="107" t="n"/>
+      <c r="D43" s="107" t="n"/>
+      <c r="E43" s="108" t="n"/>
+      <c r="F43" s="109" t="n"/>
+      <c r="G43" s="108" t="n"/>
+      <c r="H43" s="106" t="n"/>
+      <c r="I43" s="108" t="n"/>
+      <c r="J43" s="106" t="n"/>
+      <c r="K43" s="107" t="n"/>
+      <c r="L43" s="108" t="n"/>
     </row>
     <row r="44" ht="24" customHeight="1" s="27">
-      <c r="A44" s="41" t="n">
+      <c r="A44" s="105" t="n">
         <v>19</v>
       </c>
-      <c r="B44" s="16" t="n"/>
-      <c r="C44" s="17" t="n"/>
-      <c r="D44" s="17" t="n"/>
-      <c r="E44" s="18" t="n"/>
-      <c r="F44" s="41" t="n"/>
-      <c r="G44" s="18" t="n"/>
-      <c r="H44" s="16" t="n"/>
-      <c r="I44" s="18" t="n"/>
-      <c r="J44" s="43" t="n"/>
-      <c r="K44" s="17" t="n"/>
-      <c r="L44" s="18" t="n"/>
+      <c r="B44" s="106" t="n"/>
+      <c r="C44" s="107" t="n"/>
+      <c r="D44" s="107" t="n"/>
+      <c r="E44" s="108" t="n"/>
+      <c r="F44" s="109" t="n"/>
+      <c r="G44" s="108" t="n"/>
+      <c r="H44" s="106" t="n"/>
+      <c r="I44" s="108" t="n"/>
+      <c r="J44" s="106" t="n"/>
+      <c r="K44" s="107" t="n"/>
+      <c r="L44" s="108" t="n"/>
     </row>
     <row r="45" ht="24" customHeight="1" s="27">
-      <c r="A45" s="41" t="n">
+      <c r="A45" s="105" t="n">
         <v>20</v>
       </c>
-      <c r="B45" s="16" t="n"/>
-      <c r="C45" s="17" t="n"/>
-      <c r="D45" s="17" t="n"/>
-      <c r="E45" s="18" t="n"/>
-      <c r="F45" s="41" t="n"/>
-      <c r="G45" s="18" t="n"/>
-      <c r="H45" s="16" t="n"/>
-      <c r="I45" s="18" t="n"/>
-      <c r="J45" s="43" t="n"/>
-      <c r="K45" s="17" t="n"/>
-      <c r="L45" s="18" t="n"/>
+      <c r="B45" s="106" t="n"/>
+      <c r="C45" s="107" t="n"/>
+      <c r="D45" s="107" t="n"/>
+      <c r="E45" s="108" t="n"/>
+      <c r="F45" s="109" t="n"/>
+      <c r="G45" s="108" t="n"/>
+      <c r="H45" s="106" t="n"/>
+      <c r="I45" s="108" t="n"/>
+      <c r="J45" s="106" t="n"/>
+      <c r="K45" s="107" t="n"/>
+      <c r="L45" s="108" t="n"/>
     </row>
     <row r="46" ht="19.95" customHeight="1" s="27">
       <c r="A46" s="86" t="inlineStr">
@@ -2067,11 +2117,11 @@
         <v/>
       </c>
       <c r="G46" s="22" t="n"/>
-      <c r="H46" s="24" t="n"/>
-      <c r="I46" s="25" t="n"/>
-      <c r="J46" s="25" t="n"/>
-      <c r="K46" s="25" t="n"/>
-      <c r="L46" s="22" t="n"/>
+      <c r="H46" s="97" t="n"/>
+      <c r="I46" s="98" t="n"/>
+      <c r="J46" s="98" t="n"/>
+      <c r="K46" s="98" t="n"/>
+      <c r="L46" s="99" t="n"/>
     </row>
     <row r="47" ht="16.5" customHeight="1" s="27">
       <c r="A47" s="77" t="inlineStr">
@@ -2092,18 +2142,18 @@
       <c r="L47" s="18" t="n"/>
     </row>
     <row r="48" ht="43.95" customHeight="1" s="27">
-      <c r="A48" s="40" t="n"/>
-      <c r="B48" s="25" t="n"/>
-      <c r="C48" s="25" t="n"/>
-      <c r="D48" s="25" t="n"/>
-      <c r="E48" s="25" t="n"/>
-      <c r="F48" s="25" t="n"/>
-      <c r="G48" s="25" t="n"/>
-      <c r="H48" s="25" t="n"/>
-      <c r="I48" s="25" t="n"/>
-      <c r="J48" s="25" t="n"/>
-      <c r="K48" s="25" t="n"/>
-      <c r="L48" s="22" t="n"/>
+      <c r="A48" s="104" t="n"/>
+      <c r="B48" s="98" t="n"/>
+      <c r="C48" s="98" t="n"/>
+      <c r="D48" s="98" t="n"/>
+      <c r="E48" s="98" t="n"/>
+      <c r="F48" s="98" t="n"/>
+      <c r="G48" s="98" t="n"/>
+      <c r="H48" s="98" t="n"/>
+      <c r="I48" s="98" t="n"/>
+      <c r="J48" s="98" t="n"/>
+      <c r="K48" s="98" t="n"/>
+      <c r="L48" s="99" t="n"/>
     </row>
     <row r="49" ht="16.5" customHeight="1" s="27">
       <c r="A49" s="77" t="inlineStr">
@@ -2156,24 +2206,24 @@
         </is>
       </c>
       <c r="B51" s="18" t="n"/>
-      <c r="C51" s="19" t="n"/>
-      <c r="D51" s="18" t="n"/>
+      <c r="C51" s="106" t="n"/>
+      <c r="D51" s="108" t="n"/>
       <c r="E51" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="F51" s="18" t="n"/>
-      <c r="G51" s="19" t="n"/>
-      <c r="H51" s="18" t="n"/>
+      <c r="G51" s="106" t="n"/>
+      <c r="H51" s="108" t="n"/>
       <c r="I51" s="82" t="inlineStr">
         <is>
           <t>Firma:</t>
         </is>
       </c>
       <c r="J51" s="18" t="n"/>
-      <c r="K51" s="19" t="n"/>
-      <c r="L51" s="18" t="n"/>
+      <c r="K51" s="106" t="n"/>
+      <c r="L51" s="108" t="n"/>
     </row>
     <row r="52" ht="21" customHeight="1" s="27">
       <c r="A52" s="82" t="inlineStr">
@@ -2182,24 +2232,24 @@
         </is>
       </c>
       <c r="B52" s="18" t="n"/>
-      <c r="C52" s="19" t="n"/>
-      <c r="D52" s="18" t="n"/>
+      <c r="C52" s="106" t="n"/>
+      <c r="D52" s="108" t="n"/>
       <c r="E52" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="F52" s="18" t="n"/>
-      <c r="G52" s="19" t="n"/>
-      <c r="H52" s="18" t="n"/>
+      <c r="G52" s="106" t="n"/>
+      <c r="H52" s="108" t="n"/>
       <c r="I52" s="82" t="inlineStr">
         <is>
           <t>Nombre:</t>
         </is>
       </c>
       <c r="J52" s="18" t="n"/>
-      <c r="K52" s="19" t="n"/>
-      <c r="L52" s="18" t="n"/>
+      <c r="K52" s="106" t="n"/>
+      <c r="L52" s="108" t="n"/>
     </row>
     <row r="53" ht="21" customHeight="1" s="27">
       <c r="A53" s="82" t="inlineStr">
@@ -2208,24 +2258,24 @@
         </is>
       </c>
       <c r="B53" s="18" t="n"/>
-      <c r="C53" s="19" t="n"/>
-      <c r="D53" s="18" t="n"/>
+      <c r="C53" s="106" t="n"/>
+      <c r="D53" s="108" t="n"/>
       <c r="E53" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="F53" s="18" t="n"/>
-      <c r="G53" s="19" t="n"/>
-      <c r="H53" s="18" t="n"/>
+      <c r="G53" s="106" t="n"/>
+      <c r="H53" s="108" t="n"/>
       <c r="I53" s="82" t="inlineStr">
         <is>
           <t>Cargo:</t>
         </is>
       </c>
       <c r="J53" s="18" t="n"/>
-      <c r="K53" s="19" t="n"/>
-      <c r="L53" s="18" t="n"/>
+      <c r="K53" s="106" t="n"/>
+      <c r="L53" s="108" t="n"/>
     </row>
     <row r="54">
       <c r="A54" s="1" t="inlineStr">
@@ -2239,6 +2289,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection selectLockedCells="0" selectUnlockedCells="0" sheet="1" objects="0" insertRows="1" insertHyperlinks="1" autoFilter="1" scenarios="0" formatColumns="0" deleteColumns="1" insertColumns="1" pivotTables="1" deleteRows="1" formatCells="1" formatRows="0" sort="1"/>
   <mergeCells count="164">
     <mergeCell ref="H35:I35"/>
     <mergeCell ref="C23:L23"/>
